--- a/Data/joueur_equipes.xlsx
+++ b/Data/joueur_equipes.xlsx
@@ -43,43 +43,10 @@
     <x:t>Actif</x:t>
   </x:si>
   <x:si>
-    <x:t>D&amp;#xE9;fense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Défense|Cornerback</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/b4ccc481-1095-4443-9f7e-ba3b86d7866f.png</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
     <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attaque</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attaque|Centre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/photos/5e420bf7-0594-42a1-82f1-b36dc6f55d8a.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdasas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Défense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -467,7 +434,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>1</x:v>
@@ -476,135 +443,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
-      <x:c r="A4" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
-      <x:c r="A5" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
-      <x:c r="A6" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
